--- a/branches/master/ValueSet-mii-vs-consent-answer.xlsx
+++ b/branches/master/ValueSet-mii-vs-consent-answer.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:01:55+00:00</t>
+    <t>2026-09-14T20:18:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-mii-vs-consent-answer.xlsx
+++ b/branches/master/ValueSet-mii-vs-consent-answer.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:18:32+00:00</t>
+    <t>2026-09-14T20:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-mii-vs-consent-answer.xlsx
+++ b/branches/master/ValueSet-mii-vs-consent-answer.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:22:40+00:00</t>
+    <t>2026-09-14T20:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-mii-vs-consent-answer.xlsx
+++ b/branches/master/ValueSet-mii-vs-consent-answer.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:32:02+00:00</t>
+    <t>2026-09-14T21:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-mii-vs-consent-answer.xlsx
+++ b/branches/master/ValueSet-mii-vs-consent-answer.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:14:48+00:00</t>
+    <t>2026-09-16T11:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
